--- a/OpenCart-Test_Scenarios.xlsx
+++ b/OpenCart-Test_Scenarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15d74eb5e75247de/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15d74eb5e75247de/Desktop/SQA_Projects/ManualTesting_OpenCart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{C3A6A08F-4F33-41BD-9CBB-087C4849F9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC6B431E-DED7-4ACF-B753-2878D5E43EED}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{C3A6A08F-4F33-41BD-9CBB-087C4849F9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB45FABC-E6DC-4728-A52D-5A63566DBF60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2126CEF5-9B69-4BD3-AB54-1FB566E043FC}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Validate working of My Orders &gt; Your Transactions functionality</t>
   </si>
   <si>
-    <t>Validate working of My Orders &gt; Recurring Payments functionality</t>
-  </si>
-  <si>
     <t>Validate working of Affiliate functionality</t>
   </si>
   <si>
@@ -271,6 +268,9 @@
   </si>
   <si>
     <t>P3</t>
+  </si>
+  <si>
+    <t>Validate working of My Account &gt; Subscriptions</t>
   </si>
 </sst>
 </file>
@@ -744,7 +744,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>5</v>
@@ -753,13 +753,13 @@
         <v>13</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>5</v>
@@ -768,13 +768,13 @@
         <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
@@ -783,13 +783,13 @@
         <v>15</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>5</v>
@@ -798,13 +798,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
@@ -813,13 +813,13 @@
         <v>17</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -828,13 +828,13 @@
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>5</v>
@@ -843,13 +843,13 @@
         <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
@@ -858,13 +858,13 @@
         <v>20</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>5</v>
@@ -873,13 +873,13 @@
         <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>5</v>
@@ -888,13 +888,13 @@
         <v>22</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>5</v>
@@ -903,13 +903,13 @@
         <v>23</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>5</v>
@@ -918,13 +918,13 @@
         <v>24</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>5</v>
@@ -933,13 +933,13 @@
         <v>25</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>5</v>
@@ -948,13 +948,13 @@
         <v>26</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>5</v>
@@ -963,13 +963,13 @@
         <v>27</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>5</v>
@@ -978,13 +978,13 @@
         <v>28</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>5</v>
@@ -993,13 +993,13 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>5</v>
@@ -1008,13 +1008,13 @@
         <v>30</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>5</v>
@@ -1023,13 +1023,13 @@
         <v>31</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>5</v>
@@ -1038,13 +1038,13 @@
         <v>32</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>5</v>
@@ -1053,13 +1053,13 @@
         <v>33</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>5</v>
@@ -1068,13 +1068,13 @@
         <v>34</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>5</v>
@@ -1083,127 +1083,127 @@
         <v>37</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E40" s="3"/>
     </row>
